--- a/data/trans_dic/P62A$invalidez-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 23,15</t>
+          <t>5,27; 24,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 24,2</t>
+          <t>8,7; 25,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 18,62</t>
+          <t>3,05; 18,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,77</t>
+          <t>1,83; 16,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,78; 61,11</t>
+          <t>35,02; 60,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 14,62</t>
+          <t>3,17; 14,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 18,74</t>
+          <t>7,6; 18,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,62</t>
+          <t>0,84; 7,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 36,64</t>
+          <t>18,81; 36,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 23,23</t>
+          <t>9,35; 23,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 29,55</t>
+          <t>13,96; 30,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,64</t>
+          <t>4,89; 14,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 17,28</t>
+          <t>4,69; 18,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 22,46</t>
+          <t>7,73; 23,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 14,41</t>
+          <t>2,5; 15,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,33; 49,61</t>
+          <t>35,86; 50,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 17,93</t>
+          <t>8,76; 18,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,09; 24,14</t>
+          <t>13,3; 23,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,85</t>
+          <t>4,82; 11,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,64; 25,0</t>
+          <t>16,71; 24,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 16,57</t>
+          <t>3,95; 17,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 26,22</t>
+          <t>8,81; 26,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,79</t>
+          <t>2,27; 13,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 11,82</t>
+          <t>1,45; 12,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 14,09</t>
+          <t>1,39; 12,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,34</t>
+          <t>1,24; 11,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,96; 52,55</t>
+          <t>37,27; 53,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,57</t>
+          <t>3,3; 12,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 17,67</t>
+          <t>6,36; 17,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,43</t>
+          <t>2,27; 9,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 27,04</t>
+          <t>17,73; 27,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,36</t>
+          <t>1,37; 13,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 26,46</t>
+          <t>9,34; 24,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 20,88</t>
+          <t>6,5; 20,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 16,13</t>
+          <t>2,94; 15,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 19,92</t>
+          <t>5,94; 19,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 15,85</t>
+          <t>2,65; 15,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,38; 38,67</t>
+          <t>25,53; 39,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,28</t>
+          <t>2,95; 11,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 19,2</t>
+          <t>9,28; 19,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,18</t>
+          <t>6,21; 15,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 20,14</t>
+          <t>12,49; 20,36</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 19,72</t>
+          <t>3,91; 21,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 22,42</t>
+          <t>4,19; 22,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 22,68</t>
+          <t>6,21; 22,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 36,8</t>
+          <t>8,92; 37,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 22,32</t>
+          <t>4,1; 23,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 10,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,77; 43,4</t>
+          <t>25,3; 42,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 23,46</t>
+          <t>7,79; 23,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 18,65</t>
+          <t>5,31; 17,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 14,65</t>
+          <t>4,3; 14,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,96; 25,06</t>
+          <t>14,11; 25,02</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 25,48</t>
+          <t>8,2; 27,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 19,3</t>
+          <t>3,63; 16,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 8,08</t>
+          <t>1,2; 8,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,09</t>
+          <t>0,0; 12,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,67</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,41; 67,13</t>
+          <t>51,29; 67,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 16,63</t>
+          <t>5,36; 17,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 11,93</t>
+          <t>2,25; 11,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,67; 32,35</t>
+          <t>22,66; 32,4</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,19</t>
+          <t>3,41; 12,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 22,06</t>
+          <t>9,68; 20,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,41</t>
+          <t>2,78; 12,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,0</t>
+          <t>0,52; 5,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,06</t>
+          <t>3,93; 15,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 17,59</t>
+          <t>6,0; 18,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,07</t>
+          <t>4,18; 14,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 25,82</t>
+          <t>2,69; 26,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,03</t>
+          <t>4,55; 10,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 17,57</t>
+          <t>9,43; 17,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,41</t>
+          <t>4,37; 10,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,26</t>
+          <t>2,6; 13,24</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 20,77</t>
+          <t>9,11; 20,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,7; 24,77</t>
+          <t>12,55; 24,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,08; 21,55</t>
+          <t>10,88; 20,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,39</t>
+          <t>0,84; 5,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 16,84</t>
+          <t>5,16; 16,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 20,42</t>
+          <t>8,4; 19,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91; 16,65</t>
+          <t>6,91; 17,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,01; 48,11</t>
+          <t>37,4; 48,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,81; 17,48</t>
+          <t>9,0; 16,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 20,23</t>
+          <t>12,11; 20,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,21; 17,63</t>
+          <t>10,4; 17,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,67; 23,99</t>
+          <t>17,75; 24,21</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,21</t>
+          <t>7,73; 12,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,9; 19,28</t>
+          <t>13,69; 19,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,11</t>
+          <t>7,95; 11,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,26</t>
+          <t>0,81; 2,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,58</t>
+          <t>6,11; 10,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,12</t>
+          <t>8,26; 13,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,26</t>
+          <t>5,48; 9,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,15; 40,27</t>
+          <t>16,01; 40,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,81</t>
+          <t>7,66; 10,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,9; 15,59</t>
+          <t>12,03; 15,58</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,31</t>
+          <t>7,28; 10,17</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,43; 20,05</t>
+          <t>11,42; 20,11</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2457; 12219</t>
+          <t>2782; 12754</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6420; 18412</t>
+          <t>6619; 19082</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1322</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1937</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2075; 12811</t>
+          <t>2097; 12927</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>963; 9222</t>
+          <t>1004; 9047</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10830; 19028</t>
+          <t>10903; 18949</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2424; 12908</t>
+          <t>2801; 13057</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10680; 27147</t>
+          <t>11011; 26742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>978; 9758</t>
+          <t>948; 8740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10314; 20292</t>
+          <t>10419; 20179</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11113; 28096</t>
+          <t>11302; 27945</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18989; 39104</t>
+          <t>18480; 39750</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7194; 20272</t>
+          <t>7261; 21385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1860</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3751; 13689</t>
+          <t>3718; 14273</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6515; 19966</t>
+          <t>6868; 21103</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3003; 13206</t>
+          <t>2295; 13864</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43117; 60535</t>
+          <t>43756; 61273</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17193; 35890</t>
+          <t>17522; 36881</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28951; 53416</t>
+          <t>29424; 53004</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11392; 28472</t>
+          <t>11585; 28614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42739; 64212</t>
+          <t>42913; 63388</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2104; 12383</t>
+          <t>2955; 13363</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6775; 21568</t>
+          <t>7247; 22138</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2053; 12406</t>
+          <t>2045; 12126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4214</t>
+          <t>0; 4184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>970; 7858</t>
+          <t>963; 8019</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1062; 10648</t>
+          <t>1053; 9635</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1005; 9057</t>
+          <t>992; 8920</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30945; 43995</t>
+          <t>31204; 45148</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4034; 16330</t>
+          <t>4652; 17179</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10240; 27889</t>
+          <t>10033; 27509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4147; 17707</t>
+          <t>3850; 16210</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30103; 47465</t>
+          <t>31121; 48058</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>974; 9351</t>
+          <t>957; 9624</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9687; 27090</t>
+          <t>9565; 25511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6658; 20163</t>
+          <t>6277; 19989</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1443</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1883; 10459</t>
+          <t>1906; 9760</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6513; 20061</t>
+          <t>5979; 19844</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2084; 12275</t>
+          <t>2054; 11986</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20479; 31202</t>
+          <t>20603; 31591</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3982; 15211</t>
+          <t>3977; 15458</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19353; 38998</t>
+          <t>18841; 39121</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10976; 26409</t>
+          <t>10801; 27242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20009; 32166</t>
+          <t>19942; 32517</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1710; 8926</t>
+          <t>1769; 9760</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2029; 11200</t>
+          <t>2093; 11362</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4043; 15133</t>
+          <t>4145; 15159</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2989; 12859</t>
+          <t>3117; 13049</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1943; 10495</t>
+          <t>1928; 11110</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5777</t>
+          <t>0; 6193</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10733; 18079</t>
+          <t>10538; 17743</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6516; 18820</t>
+          <t>6247; 18510</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5280; 18089</t>
+          <t>5151; 17445</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5094; 18154</t>
+          <t>5333; 18469</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10201; 18309</t>
+          <t>10308; 18277</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1834</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6056; 18939</t>
+          <t>6092; 20410</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2991; 14267</t>
+          <t>2685; 12499</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>955; 6462</t>
+          <t>960; 6922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6220</t>
+          <t>0; 6155</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6411</t>
+          <t>0; 6488</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2169</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30815; 40233</t>
+          <t>30740; 40407</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6537</t>
+          <t>0; 7162</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7284; 22354</t>
+          <t>7209; 23187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2957; 14103</t>
+          <t>2655; 13624</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31712; 45251</t>
+          <t>31699; 45313</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4655; 17408</t>
+          <t>4876; 17161</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15201; 35099</t>
+          <t>15401; 33377</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4293; 17529</t>
+          <t>4279; 19001</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>837; 7928</t>
+          <t>828; 8859</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4701; 16722</t>
+          <t>4675; 18598</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8925; 26417</t>
+          <t>9011; 27675</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6630; 23005</t>
+          <t>6380; 21418</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9543; 88808</t>
+          <t>9247; 89455</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11415; 28867</t>
+          <t>11917; 28620</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28578; 54350</t>
+          <t>29148; 53520</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12821; 31894</t>
+          <t>13387; 33383</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11652; 66629</t>
+          <t>13077; 66542</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15804; 34930</t>
+          <t>15325; 34547</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24720; 48229</t>
+          <t>24439; 47433</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23662; 46035</t>
+          <t>23232; 44544</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1672; 10875</t>
+          <t>1686; 10236</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6634; 21668</t>
+          <t>6645; 21547</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13217; 31629</t>
+          <t>13008; 30362</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12358; 29785</t>
+          <t>12371; 30519</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64590; 83948</t>
+          <t>65265; 85048</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>26144; 51892</t>
+          <t>26703; 50120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41515; 70698</t>
+          <t>42323; 70776</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40084; 69192</t>
+          <t>40818; 69563</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>66469; 90235</t>
+          <t>66751; 91051</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>56950; 90081</t>
+          <t>57073; 90981</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>121069; 167919</t>
+          <t>119227; 166327</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70139; 109097</t>
+          <t>71692; 106875</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5744; 18124</t>
+          <t>6516; 18862</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>34552; 60976</t>
+          <t>35221; 63012</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>62587; 97897</t>
+          <t>61610; 97220</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39438; 68248</t>
+          <t>40367; 72055</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>142082; 377571</t>
+          <t>150140; 379394</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>101582; 142040</t>
+          <t>100677; 140889</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>192494; 252181</t>
+          <t>194534; 252031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>119920; 168861</t>
+          <t>119274; 166609</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>198735; 348746</t>
+          <t>198670; 349740</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$invalidez-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Provincia-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 24,16</t>
+          <t>4,57; 24,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 25,08</t>
+          <t>8,81; 25,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 18,79</t>
+          <t>3,04; 18,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,46</t>
+          <t>1,77; 15,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,02; 60,85</t>
+          <t>37,33; 61,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,79</t>
+          <t>2,93; 14,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 18,46</t>
+          <t>7,11; 18,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,72</t>
+          <t>0,85; 8,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,81; 36,43</t>
+          <t>19,31; 37,21</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 23,11</t>
+          <t>9,44; 23,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 30,03</t>
+          <t>13,88; 28,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 14,39</t>
+          <t>4,67; 14,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 18,02</t>
+          <t>4,68; 17,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 23,74</t>
+          <t>7,17; 22,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,13</t>
+          <t>2,49; 13,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,86; 50,21</t>
+          <t>37,24; 51,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 18,43</t>
+          <t>8,65; 18,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 23,96</t>
+          <t>12,72; 24,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,91</t>
+          <t>4,92; 12,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 24,68</t>
+          <t>16,48; 24,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 17,88</t>
+          <t>2,81; 17,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 26,92</t>
+          <t>7,73; 25,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 13,48</t>
+          <t>2,31; 14,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,06</t>
+          <t>1,46; 11,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,75</t>
+          <t>1,38; 12,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,16</t>
+          <t>1,26; 12,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,27; 53,92</t>
+          <t>36,69; 52,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,17</t>
+          <t>2,99; 11,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 17,43</t>
+          <t>6,37; 17,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,54</t>
+          <t>2,44; 9,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 27,38</t>
+          <t>17,38; 26,65</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,75</t>
+          <t>1,37; 12,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 24,92</t>
+          <t>9,24; 24,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 20,7</t>
+          <t>6,62; 21,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 15,05</t>
+          <t>2,85; 15,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,71</t>
+          <t>6,44; 20,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,48</t>
+          <t>2,59; 14,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,53; 39,15</t>
+          <t>25,44; 39,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,46</t>
+          <t>2,85; 11,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 19,26</t>
+          <t>8,99; 19,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,66</t>
+          <t>6,48; 15,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 20,36</t>
+          <t>12,15; 19,75</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 21,56</t>
+          <t>3,88; 20,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 22,74</t>
+          <t>4,23; 22,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 22,72</t>
+          <t>6,08; 24,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 37,34</t>
+          <t>8,4; 36,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 23,63</t>
+          <t>3,98; 23,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,83</t>
+          <t>0,0; 11,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,3; 42,59</t>
+          <t>25,47; 42,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 23,08</t>
+          <t>7,64; 22,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,99</t>
+          <t>5,29; 18,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,9</t>
+          <t>4,53; 14,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,11; 25,02</t>
+          <t>13,88; 24,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -1422,27 +1422,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 27,46</t>
+          <t>8,1; 26,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,9</t>
+          <t>3,74; 18,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,66</t>
+          <t>1,22; 7,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,95</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 10,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,29; 67,42</t>
+          <t>51,92; 67,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 17,25</t>
+          <t>5,32; 16,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 11,52</t>
+          <t>2,32; 11,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,66; 32,4</t>
+          <t>23,04; 32,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,01</t>
+          <t>3,25; 11,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 20,98</t>
+          <t>9,73; 21,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,36</t>
+          <t>2,77; 11,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,58</t>
+          <t>0,44; 5,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 15,64</t>
+          <t>4,13; 15,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 18,43</t>
+          <t>5,58; 18,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 14,03</t>
+          <t>4,13; 14,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 26,01</t>
+          <t>17,88; 28,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,93</t>
+          <t>4,63; 10,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,43; 17,31</t>
+          <t>9,18; 17,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,9</t>
+          <t>4,45; 10,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 13,24</t>
+          <t>9,03; 14,75</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,11; 20,55</t>
+          <t>8,89; 19,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,55; 24,36</t>
+          <t>12,14; 23,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,88; 20,86</t>
+          <t>11,1; 21,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,08</t>
+          <t>0,66; 5,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 16,75</t>
+          <t>5,8; 16,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,4; 19,61</t>
+          <t>8,48; 19,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91; 17,06</t>
+          <t>7,05; 17,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,4; 48,74</t>
+          <t>36,49; 47,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,89</t>
+          <t>8,68; 16,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,11; 20,25</t>
+          <t>12,29; 20,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,4; 17,72</t>
+          <t>10,38; 17,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,75; 24,21</t>
+          <t>18,04; 24,46</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,33</t>
+          <t>7,89; 12,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,09</t>
+          <t>13,92; 19,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,86</t>
+          <t>7,98; 11,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,35</t>
+          <t>0,73; 2,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,94</t>
+          <t>6,18; 10,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,03</t>
+          <t>8,36; 13,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,78</t>
+          <t>5,51; 9,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,01; 40,46</t>
+          <t>36,25; 41,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,72</t>
+          <t>7,56; 10,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,03; 15,58</t>
+          <t>11,99; 15,68</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,17</t>
+          <t>7,21; 10,02</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,11</t>
+          <t>17,84; 20,89</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15537</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2782; 12754</t>
+          <t>2411; 12672</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6619; 19082</t>
+          <t>6703; 19638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2097; 12927</t>
+          <t>2093; 12642</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1004; 9047</t>
+          <t>972; 8377</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10903; 18949</t>
+          <t>11709; 19416</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2801; 13057</t>
+          <t>2586; 12425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11011; 26742</t>
+          <t>10303; 26301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>948; 8740</t>
+          <t>962; 9492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10419; 20179</t>
+          <t>10946; 21086</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52542</t>
+          <t>55598</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52542</t>
+          <t>55598</t>
         </is>
       </c>
     </row>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11302; 27945</t>
+          <t>11411; 28676</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18480; 39750</t>
+          <t>18364; 38081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7261; 21385</t>
+          <t>6937; 21243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2437,42 +2437,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3718; 14273</t>
+          <t>3705; 14187</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6868; 21103</t>
+          <t>6374; 19801</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2295; 13864</t>
+          <t>2282; 12585</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43756; 61273</t>
+          <t>47294; 64826</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17522; 36881</t>
+          <t>17314; 36506</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29424; 53004</t>
+          <t>28147; 53796</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11585; 28614</t>
+          <t>11809; 29311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42913; 63388</t>
+          <t>44506; 66703</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>38776</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2955; 13363</t>
+          <t>2101; 12973</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7247; 22138</t>
+          <t>6359; 20604</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2045; 12126</t>
+          <t>2079; 13156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4184</t>
+          <t>0; 4684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>963; 8019</t>
+          <t>968; 7742</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1053; 9635</t>
+          <t>1040; 9394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>992; 8920</t>
+          <t>1008; 10129</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31204; 45148</t>
+          <t>31595; 45390</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4652; 17179</t>
+          <t>4218; 16090</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10033; 27509</t>
+          <t>10047; 27016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3850; 16210</t>
+          <t>4152; 16741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31121; 48058</t>
+          <t>30630; 46957</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>27422</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>957; 9624</t>
+          <t>957; 8659</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9565; 25511</t>
+          <t>9462; 24983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6277; 19989</t>
+          <t>6390; 20396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,42 +2853,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1906; 9760</t>
+          <t>1849; 9936</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5979; 19844</t>
+          <t>6488; 20415</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2054; 11986</t>
+          <t>2005; 11539</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20603; 31591</t>
+          <t>21893; 33573</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3977; 15458</t>
+          <t>3845; 15255</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18841; 39121</t>
+          <t>18248; 38716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10801; 27242</t>
+          <t>11276; 27811</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19942; 32517</t>
+          <t>21255; 34555</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>14518</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1769; 9760</t>
+          <t>1756; 9211</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2093; 11362</t>
+          <t>2113; 11339</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4145; 15159</t>
+          <t>4056; 16054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3117; 13049</t>
+          <t>2937; 12639</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1928; 11110</t>
+          <t>1871; 11187</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6193</t>
+          <t>0; 6695</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10538; 17743</t>
+          <t>11019; 18438</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6247; 18510</t>
+          <t>6131; 18327</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5151; 17445</t>
+          <t>5133; 18134</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5333; 18469</t>
+          <t>5609; 18168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10308; 18277</t>
+          <t>10647; 18996</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>39077</t>
         </is>
       </c>
     </row>
@@ -3254,27 +3254,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6092; 20410</t>
+          <t>6021; 19324</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2685; 12499</t>
+          <t>2763; 13956</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>960; 6922</t>
+          <t>967; 5804</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6155</t>
+          <t>0; 6179</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6488</t>
+          <t>0; 6343</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30740; 40407</t>
+          <t>31827; 41441</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7162</t>
+          <t>0; 6107</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7209; 23187</t>
+          <t>7154; 22349</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2655; 13624</t>
+          <t>2742; 13266</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31699; 45313</t>
+          <t>32351; 45801</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>33555</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>41718</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4876; 17161</t>
+          <t>4635; 16284</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15401; 33377</t>
+          <t>15487; 33915</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4279; 19001</t>
+          <t>4254; 18200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>828; 8859</t>
+          <t>846; 9773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4675; 18598</t>
+          <t>4916; 18100</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9011; 27675</t>
+          <t>8372; 27420</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6380; 21418</t>
+          <t>6302; 21619</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9247; 89455</t>
+          <t>30146; 48298</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11917; 28620</t>
+          <t>12120; 28676</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29148; 53520</t>
+          <t>28399; 53820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13387; 33383</t>
+          <t>13633; 33302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13077; 66542</t>
+          <t>32431; 52941</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>85141</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78632</t>
+          <t>90202</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15325; 34547</t>
+          <t>14943; 33371</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24439; 47433</t>
+          <t>23639; 46360</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23232; 44544</t>
+          <t>23715; 46181</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1686; 10236</t>
+          <t>1481; 11844</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6645; 21547</t>
+          <t>7463; 21762</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13008; 30362</t>
+          <t>13132; 30715</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12371; 30519</t>
+          <t>12615; 31025</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>65265; 85048</t>
+          <t>73034; 95451</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>26703; 50120</t>
+          <t>25770; 48704</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42323; 70776</t>
+          <t>42959; 71635</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40818; 69563</t>
+          <t>40745; 70341</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>66751; 91051</t>
+          <t>76517; 103762</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>288348</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>299495</t>
+          <t>322848</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>57073; 90981</t>
+          <t>58227; 90227</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119227; 166327</t>
+          <t>121248; 166025</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71692; 106875</t>
+          <t>71919; 107131</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6516; 18862</t>
+          <t>6342; 19634</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>35221; 63012</t>
+          <t>35608; 60881</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>61610; 97220</t>
+          <t>62373; 98199</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40367; 72055</t>
+          <t>40608; 70976</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>150140; 379394</t>
+          <t>291430; 332244</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100677; 140889</t>
+          <t>99271; 142305</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>194534; 252031</t>
+          <t>193943; 253555</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>119274; 166609</t>
+          <t>118089; 164143</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>198670; 349740</t>
+          <t>299363; 350622</t>
         </is>
       </c>
     </row>
